--- a/2313.HK.xlsx
+++ b/2313.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5BE72B-E2A8-4537-A7C9-244C0081CC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE594FA-39BE-4EED-A319-58780E59A771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{018E0477-05D3-47A6-BBAA-907DACD6F8C2}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{018E0477-05D3-47A6-BBAA-907DACD6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>Shenzou International</t>
   </si>
@@ -159,9 +159,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Q225</t>
-  </si>
-  <si>
     <t>4 Big Costumers:</t>
   </si>
   <si>
@@ -221,6 +218,15 @@
   <si>
     <t>and specialized components e.g. for Nike</t>
   </si>
+  <si>
+    <t>H126</t>
+  </si>
+  <si>
+    <t>H226</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
 </sst>
 </file>
 
@@ -229,13 +235,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -318,34 +330,37 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -702,7 +717,7 @@
         <v>35</v>
       </c>
       <c r="J2" s="2">
-        <v>47.12</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -711,7 +726,7 @@
       </c>
       <c r="J3" s="10">
         <f>+J2*J10</f>
-        <v>41.465599999999995</v>
+        <v>31.204800000000002</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -721,8 +736,8 @@
       <c r="J4" s="3">
         <v>1503.222397</v>
       </c>
-      <c r="K4" s="11" t="s">
-        <v>40</v>
+      <c r="K4" s="18" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -734,7 +749,7 @@
       </c>
       <c r="J5" s="3">
         <f>+J3*J4</f>
-        <v>62332.018625043194</v>
+        <v>46907.754253905601</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -745,11 +760,11 @@
         <v>13</v>
       </c>
       <c r="J6" s="3">
-        <f>15117.148+10320.273</f>
-        <v>25437.420999999998</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>40</v>
+        <f>202.802+15279.98+11297.186</f>
+        <v>26779.968000000001</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -757,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="J7" s="3">
-        <v>14701.28</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>40</v>
+        <v>197</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -769,7 +784,7 @@
       </c>
       <c r="J8" s="3">
         <f>+J5-J6+J7</f>
-        <v>51595.877625043198</v>
+        <v>20324.7862539056</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -779,7 +794,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>36</v>
@@ -790,16 +805,16 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J12" s="3">
         <v>101720</v>
@@ -807,21 +822,21 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="8">
         <v>4333.0709999999999</v>
@@ -831,12 +846,12 @@
         <v>0.28952023414607025</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="8">
         <v>3435.558</v>
@@ -846,12 +861,12 @@
         <v>0.22955164052987015</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="8">
         <v>2992.45</v>
@@ -861,12 +876,12 @@
         <v>0.19994475619494995</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18" s="8">
         <v>1532.2090000000001</v>
@@ -876,12 +891,12 @@
         <v>0.10237669967575334</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" s="13">
         <f>+SUM(D15:D18)</f>
@@ -940,6 +955,12 @@
       <c r="J2" s="11" t="s">
         <v>38</v>
       </c>
+      <c r="K2" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
@@ -960,7 +981,9 @@
         <v>10128.585999999999</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>9041.8330000000005</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -999,7 +1022,9 @@
         <v>3792.1329999999998</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>3962.8629999999998</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1038,7 +1063,9 @@
         <v>940.21100000000001</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>997.75199999999995</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -1077,7 +1104,9 @@
         <v>105.45399999999999</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>176.72900000000001</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -1130,7 +1159,9 @@
         <v>14966.384</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="7">
+        <v>14179.177</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1169,7 +1200,9 @@
         <v>10908.366</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>10981.713</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -1215,15 +1248,21 @@
         <v>3761.469000000001</v>
       </c>
       <c r="H9" s="3">
-        <f t="shared" ref="H9:I9" si="3">+H7-H8</f>
+        <f t="shared" ref="H9:K9" si="3">+H7-H8</f>
         <v>0</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="3"/>
         <v>4058.018</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="3"/>
+        <v>3197.4639999999999</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1262,7 +1301,9 @@
         <v>799.39700000000005</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>681.35500000000002</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -1301,7 +1342,9 @@
         <v>108.75700000000001</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>123.086</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -1340,7 +1383,9 @@
         <v>1081.8</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>1064.184</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -1386,15 +1431,21 @@
         <v>3368.3980000000006</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" ref="H13:I13" si="5">+H9+H10-SUM(H11:H12)</f>
+        <f t="shared" ref="H13:K13" si="5">+H9+H10-SUM(H11:H12)</f>
         <v>0</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="5"/>
         <v>3666.8580000000002</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="J13" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="5"/>
+        <v>2691.549</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
@@ -1433,7 +1484,9 @@
         <v>175.886</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>156.01900000000001</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -1472,7 +1525,9 @@
         <v>139.196</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>-497.09500000000003</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1511,7 +1566,9 @@
         <v>1.952</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3">
+        <v>1.4390000000000001</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1557,15 +1614,21 @@
         <v>3249.2090000000003</v>
       </c>
       <c r="H17" s="3">
-        <f t="shared" ref="H17:I17" si="7">+H13-H14+H15+H16</f>
+        <f t="shared" ref="H17:K17" si="7">+H13-H14+H15+H16</f>
         <v>0</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="7"/>
         <v>3632.1200000000003</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="J17" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="7"/>
+        <v>2039.8739999999998</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -1604,7 +1667,9 @@
         <v>455.28399999999999</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3">
+        <v>135.31100000000001</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -1650,15 +1715,21 @@
         <v>2931.0280000000002</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" ref="H19:I19" si="9">+H17-H18</f>
+        <f t="shared" ref="H19:K19" si="9">+H17-H18</f>
         <v>0</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="9"/>
         <v>3176.8360000000002</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="J19" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="9"/>
+        <v>1904.5629999999999</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -1726,7 +1797,7 @@
         <v>1.4148465351797168</v>
       </c>
       <c r="F21" s="8" t="e">
-        <f t="shared" ref="F21:I21" si="11">+F19/F22</f>
+        <f t="shared" ref="F21:K21" si="11">+F19/F22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="8">
@@ -1741,8 +1812,14 @@
         <f t="shared" si="11"/>
         <v>2.1133506301795744</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="J21" s="8" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="11"/>
+        <v>1.2669868435974347</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -1781,7 +1858,9 @@
         <v>1503.222397</v>
       </c>
       <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="K22" s="3">
+        <v>1503.222397</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -1864,7 +1943,7 @@
     </row>
     <row r="25" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -1888,8 +1967,14 @@
         <f>+I7/G7-1</f>
         <v>0.15339222012749554</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="J25" s="16" t="e">
+        <f t="shared" ref="J25:K25" si="12">+J7/H7-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="16">
+        <f t="shared" si="12"/>
+        <v>-5.2598343060020425E-2</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -1912,7 +1997,7 @@
     </row>
     <row r="26" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B26" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -1936,8 +2021,14 @@
         <f>+I9/I7</f>
         <v>0.27114218103718307</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="J26" s="14" t="e">
+        <f t="shared" ref="J26:K26" si="13">+J9/J7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="14">
+        <f t="shared" si="13"/>
+        <v>0.22550420239482163</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -1960,7 +2051,7 @@
     </row>
     <row r="27" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1984,8 +2075,14 @@
         <f>+I13/I7</f>
         <v>0.24500627539691619</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="J27" s="14" t="e">
+        <f t="shared" ref="J27:K27" si="14">+J13/J7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="14"/>
+        <v>0.18982406383670927</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -2008,7 +2105,7 @@
     </row>
     <row r="28" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B28" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -2032,8 +2129,14 @@
         <f>+I18/I17</f>
         <v>0.12534938272964549</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
+      <c r="J28" s="14" t="e">
+        <f t="shared" ref="J28:K28" si="15">+J18/J17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="14">
+        <f t="shared" si="15"/>
+        <v>6.6333018608012079E-2</v>
+      </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
